--- a/ADCS/Magnetourqers/Magnetourqer.xlsx
+++ b/ADCS/Magnetourqers/Magnetourqer.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Main Engineering\Engineering\Project Genesis EE Notes\ADCS\Magnetourqers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A183590-C69C-4414-9898-206BFCAEF07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62916E15-92BF-4931-8A44-CCA69B9BEF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hand Calcs for Coil" sheetId="1" r:id="rId1"/>
+    <sheet name="H-Bridge Design" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>m</t>
   </si>
@@ -108,6 +109,18 @@
   </si>
   <si>
     <t>kg m^2</t>
+  </si>
+  <si>
+    <t>DRV8876</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/DRV8876PWPR/10270213</t>
+  </si>
+  <si>
+    <t>Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -40-125</t>
   </si>
 </sst>
 </file>
@@ -738,4 +751,33 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E125EC9C-47F3-49A3-9792-FDA20251E161}">
+  <dimension ref="C4:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="8.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>